--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\reiya\seminar\virtual-browser\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18D94119-0CBF-49B5-A4CD-1E503AAC7AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3577E355-6EFF-4ADB-BE9C-349DEDDBC7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5932FA94-6FAB-4458-BFF3-7F68B76D0284}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="normal" sheetId="1" r:id="rId1"/>
+    <sheet name="viewport" sheetId="2" r:id="rId2"/>
+    <sheet name="lcp" sheetId="3" r:id="rId3"/>
+    <sheet name="result" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>https://www.google.com/</t>
     <phoneticPr fontId="2"/>
@@ -162,19 +165,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>128kbps</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>200kbps</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>300kbps</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>1024kbps</t>
+    <t>平均</t>
+    <rPh sb="0" eb="2">
+      <t>ヘイキン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -578,113 +572,126 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603E50D8-3873-4C52-8DE4-1A036E3C7CAD}">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:AA31"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="35.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>31</v>
+      <c r="B1" s="2">
+        <v>1</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
-        <v>32</v>
+      <c r="G1" s="2">
+        <v>2</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="2" t="s">
-        <v>33</v>
+      <c r="L1" s="2">
+        <v>3</v>
       </c>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
-      <c r="Q1" s="2" t="s">
-        <v>34</v>
+      <c r="Q1" s="2">
+        <v>4</v>
       </c>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+      <c r="V1" s="2">
+        <v>5</v>
+      </c>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+      <c r="AA1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -765,11 +772,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="V1:Z1"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
@@ -806,4 +814,34 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC84C3AD-2814-46C8-A529-A7CE2AE9CE31}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData/>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F261F572-2382-4D28-9214-1DE8C807B89B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData/>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBEB08FA-FEF2-4D8B-891D-A9344EEA79D8}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData/>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>